--- a/Code/democracy_index.xlsx
+++ b/Code/democracy_index.xlsx
@@ -127,7 +127,7 @@
     <t>Norge</t>
   </si>
   <si>
-    <t>Lichtenstein (ingen FN-tall/konservativt estimat)</t>
+    <t>Lichtenstein (ingen FN-tall/konservativt estimat/ref. Freedom House)</t>
   </si>
   <si>
     <t>Island</t>
